--- a/data_extactor/batch_10_fa/trimmed/batch_0029_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0029_fa_trim.xlsx
@@ -508,12 +508,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | تفکر انتقادی | نگارش | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتریان و خدمات فردی | آموزش و پرورش | جامعه‌شناسی و مردم‌شناسی | پزشکی و دندان‌پزشکی</t>
+          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | آموزش و پرورش | جامعه‌شناسی و انسان‌شناسی | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوره | مددکاران اجتماعی بخش سلامت | درمانگران ازدواج و خانواده | مشاوران سلامت روان | روان‌پزشکان | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | روان‌شناسان بالینی و مشاوران سلامت روان | مددکاران اجتماعی بخش سلامت و درمان | درمانگران ازدواج و خانواده | مشاوران سلامت روان | روان‌پزشکان | مشاوران اعتیاد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | حقوق و امور دولتی | آموزش و پرورش</t>
+          <t>درمان و مشاوره | روان‌شناسی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | قانون و دولت | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران اجتماعی بخش سلامت | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | مشاوران سلامت روان | مشاوران توان‌بخشی | دستیاران خدمات اجتماعی و انسانی | مدیران خدمات اجتماعی و عمومی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مددکاران اجتماعی بخش سلامت و درمان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | مشاوران سلامت روان | مشاوران توانبخشی | دستیاران خدمات اجتماعی و انسانی | مدیران خدمات اجتماعی و خدمات مردمی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نگارش | سخن گفتن | راهبردهای یادگیری | یادگیری فعال | درک مطلب | تفکر انتقادی | نظارت</t>
+          <t>گوش دادن فعال | نگارش | سخن گفتن | راهبردهای یادگیری | یادگیری فعال | درک مطلب | تفکر انتقادی | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | آموزش و پرورش | روان‌شناسی | جامعه‌شناسی و مردم‌شناسی | ارتباطات و رسانه | پزشکی و دندان‌پزشکی</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | ارتباطات و رسانه | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>رابطان سلامت و بهورزان | کارشناسان تغذیه و رژیم‌درمانی | مددکاران اجتماعی بخش سلامت | هماهنگ‌کنندگان برنامه‌های درسی و آموزشی | مدیران خدمات بهداشتی و درمانی | پزشکان طب پیشگیری | پرستاران دارای پروانه</t>
+          <t>رابطان سلامت و بهورزان | کارشناسان و متخصصان تغذیه و رژیم‌درمانی | مددکاران اجتماعی بخش سلامت و درمان | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | مدیران خدمات درمانی و بهداشتی | متخصصان پزشکی اجتماعی و طب پیشگیری | پرستاران</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>حقوق و امور دولتی | ایمنی و امنیت عمومی | روان‌شناسی | درمان و مشاوره | جامعه‌شناسی و مردم‌شناسی | خدمات مشتریان و خدمات فردی</t>
+          <t>قانون و دولت | ایمنی و امنیت عمومی | روان‌شناسی | درمان و مشاوره | جامعه‌شناسی و انسان‌شناسی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | زندانبانان و ماموران مراقبت زندان | کارآگاهان و بازرسان جنایی | سرپرستان رده‌اول زندانبانان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | مشاوران توان‌بخشی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | مأموران زندان و بازداشتگاه | کارآگاهان و بازرسان جنایی | سرپرستان رده‌اول ماموران مراقبت پرواز و زندان‌بانان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | مشاوران توانبخشی | مشاوران اعتیاد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | روان‌شناسی | درمان و مشاوره | امور دفتری و اداری | جامعه‌شناسی و مردم‌شناسی | آموزش و پرورش</t>
+          <t>خدمات مشتری و شخصی | روان‌شناسی | درمان و مشاوره | اداری | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | رابطان سلامت و بهورزان | مددکاران اجتماعی بخش سلامت | مشاوران سلامت روان | مراقبان خدمات فردی | مشاوران توان‌بخشی | مشاوران سوءمصرف مواد و اختلالات رفتاری</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | رابطان سلامت و بهورزان | مددکاران اجتماعی بخش سلامت و درمان | مشاوران سلامت روان | مراقبان خدمات شخصی و همراهان توان‌خواهان | مشاوران توانبخشی | مشاوران اعتیاد و اختلالات رفتاری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نگارش | درک مطلب | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | نگارش | درک مطلب | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | آموزش و پرورش | مدیریت و امور اداری | پزشکی و دندان‌پزشکی | روان‌شناسی | امور دفتری و اداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | مدیریت و اداره | پزشکی و دندان‌پزشکی | روان‌شناسی | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | کارشناسان تغذیه و رژیم‌درمانی | کارشناسان آموزش بهداشت | مددکاران اجتماعی بخش سلامت | مراقبان سلامت در منزل | پزشکان طب پیشگیری | دستیاران خدمات اجتماعی و انسانی</t>
+          <t>مددکاران اجتماعی کودک، خانواده و مدرسه | کارشناسان و متخصصان تغذیه و رژیم‌درمانی | کارشناسان آموزش بهداشت و ارتقای سلامت | مددکاران اجتماعی بخش سلامت و درمان | مراقبان سلامت و بهیاران مراقبت در منزل | متخصصان پزشکی اجتماعی و طب پیشگیری | دستیاران خدمات اجتماعی و انسانی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | درمان و مشاوره | روان‌شناسی | جامعه‌شناسی و مردم‌شناسی | آموزش و پرورش | حقوق و امور دولتی</t>
+          <t>خدمات مشتری و شخصی | درمان و مشاوره | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | آموزش و پرورش | قانون و دولت</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>دستیاران خدمات اجتماعی و انسانی | رابطان سلامت و بهورزان | کارشناسان آموزش بهداشت | مددکاران اجتماعی کودک، خانواده و مدرسه | مشاوران سلامت روان | مشاوران توان‌بخشی | مدیران خدمات اجتماعی و عمومی</t>
+          <t>دستیاران خدمات اجتماعی و انسانی | رابطان سلامت و بهورزان | کارشناسان آموزش بهداشت و ارتقای سلامت | مددکاران اجتماعی کودک، خانواده و مدرسه | مشاوران سلامت روان | مشاوران توانبخشی | مدیران خدمات اجتماعی و خدمات مردمی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>فلسفه و الهیات | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | آموزش و پرورش | درمان و مشاوره | ارتباطات و رسانه | روان‌شناسی</t>
+          <t>فلسفه و الهیات | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | درمان و مشاوره | ارتباطات و رسانه | روان‌شناسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران فعالیت‌ها و آموزش‌های مذهبی | مشاوران و راهنمایان تحصیلی و شغلی | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مدیران امور آرامستان‌ها و تشریفات تدفین | مدرسان فلسفه و الهیات در آموزش عالی | مشاوران و سرپرستان خوابگاه‌ها</t>
+          <t>مدیران فعالیت‌ها و آموزش‌های مذهبی | مشاوران تحصیلی، شغلی و هدایت استعدادها | درمانگران ازدواج و خانواده | مشاوران سلامت روان | مدیران و برگزارکنندگان مراسم تشییع و تدفین | مدرسان فلسفه و الهیات در آموزش عالی | سرپرستان و مشاوران خوابگاه</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی | یادگیری فعال | درک مطلب | راهبردهای یادگیری | نگارش | نظارت</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | درک مطلب | راهبردهای یادگیری | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>فلسفه و الهیات | آموزش و پرورش | خدمات مشتریان و خدمات فردی | روان‌شناسی | مدیریت و امور اداری | ارتباطات و رسانه</t>
+          <t>فلسفه و الهیات | آموزش و پرورش | خدمات مشتری و شخصی | روان‌شناسی | مدیریت و اداره | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>روحانیون و مبلغان مذهبی | مدیران آموزشی پیش‌دبستانی تا متوسطه | مدیران مراکز پیش‌دبستانی و مهدکودک‌ها | هماهنگ‌کنندگان برنامه‌های درسی و آموزشی | مربیان و کارشناسان فعالیت‌های اوقات فراغت | مدیران خدمات اجتماعی و عمومی | مدیران آموزش و توانمندسازی منابع انسانی</t>
+          <t>روحانیون و مبلغان مذهبی | مدیران آموزشی مقاطع ابتدایی و متوسطه | مدیران مراکز آموزشی و مراقبت از کودک، پیش‌دبستانی و مهدکودک | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | کارکنان و متصدیان امور تفریحی و اوقات فراغت | مدیران خدمات اجتماعی و خدمات مردمی | مدیران آموزش و بهسازی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>فلسفه و الهیات | خدمات مشتریان و خدمات فردی | آموزش و پرورش | روان‌شناسی | جامعه‌شناسی و مردم‌شناسی | درمان و مشاوره</t>
+          <t>فلسفه و الهیات | خدمات مشتری و شخصی | آموزش و پرورش | روان‌شناسی | جامعه‌شناسی و انسان‌شناسی | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | درک کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | درک کتبی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>روحانیون و مبلغان مذهبی | مدیران فعالیت‌ها و آموزش‌های مذهبی | سایر متخصصان خدمات اجتماعی و عمومی | دستیاران خدمات اجتماعی و انسانی | مددکاران اجتماعی کودک، خانواده و مدرسه | مشاوران و راهنمایان تحصیلی و شغلی | مدرسان فلسفه و الهیات در آموزش عالی</t>
+          <t>روحانیون و مبلغان مذهبی | مدیران فعالیت‌ها و آموزش‌های مذهبی | سایر متخصصان خدمات اجتماعی و عمومی | دستیاران خدمات اجتماعی و انسانی | مددکاران اجتماعی کودک، خانواده و مدرسه | مشاوران تحصیلی، شغلی و هدایت استعدادها | مدرسان فلسفه و الهیات در آموزش عالی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
